--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1360,7 +1360,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2762,7 +2762,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
